--- a/SPC26S1 - 04 April.xlsx
+++ b/SPC26S1 - 04 April.xlsx
@@ -2522,7 +2522,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="100">
+  <dxfs count="108">
     <dxf>
       <font>
         <color rgb="FF1F4E79"/>
@@ -3543,6 +3543,62 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9F9F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE4A0C8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3848,7 +3904,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
@@ -4023,7 +4079,127 @@
         <v>20</v>
       </c>
     </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="9"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Row colours by Claim Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="45" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each claim row is shaded by its Claim Status (column A) using conditional formatting, so the colour follows the status automatically when it is changed. Rows with no Claim Status keep their normal formatting. The deadline countdown columns keep their own colour bands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PAID - green</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Finalized - blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Received - lavender</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Pending - yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Under Review - orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Denied - red</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Rejected - pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Not found - grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Any other status is left unshaded.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A41">
+    <cfRule type="expression" dxfId="100" priority="1">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A42">
+    <cfRule type="expression" dxfId="101" priority="2">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43">
+    <cfRule type="expression" dxfId="102" priority="3">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44">
+    <cfRule type="expression" dxfId="103" priority="4">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A45">
+    <cfRule type="expression" dxfId="104" priority="5">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46">
+    <cfRule type="expression" dxfId="105" priority="6">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A47">
+    <cfRule type="expression" dxfId="106" priority="7">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48">
+    <cfRule type="expression" dxfId="107" priority="8">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5433,6 +5609,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="100" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A12" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -9160,6 +9362,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="100" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A32" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -10109,6 +10337,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="100" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A7" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -12248,6 +12502,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="100" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A18" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -14617,6 +14897,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="100" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A20" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>

--- a/SPC26S1 - 04 April.xlsx
+++ b/SPC26S1 - 04 April.xlsx
@@ -2327,7 +2327,7 @@
     <t>84 claims with a date of service in 2026-04 April, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
   </si>
   <si>
-    <t>Every specialty sheet is sorted in three groups: claims with an empty Latest Date Worked (column K) at the top, then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim goes to the bottom even when its Latest Date Worked is empty). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+    <t>Every specialty sheet is sorted in three groups: claims with an empty Latest Date Worked (column K) at the top, then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the top group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
     <t>Deadline order within each group, with the colour band each row gets, counted on 19 September 2026:</t>

--- a/SPC26S1 - 04 April.xlsx
+++ b/SPC26S1 - 04 April.xlsx
@@ -1025,7 +1025,7 @@
     <t>Past due rows sit below the claims that can still be filed on time rather than at the very top, so the actionable work stays first. That is why the numbers run up to the longest window and then restart at the negatives.</t>
   </si>
   <si>
-    <t>Filing Deadline is the date of service plus the primary payer's limit, taken from 'Carrier_Timely_Filing_Reference.xlsx'. Days Until Deadline is a live formula, so the count stays true as time passes - but the row order is a snapshot taken on 12 August 2026. Sorting on Days Until Deadline alone would mix the three groups above back together, so when you re-sort keep the empty Latest Date Worked rows first and the Finalized and PAID rows last.</t>
+    <t>Filing Deadline is the date of service plus the primary payer's limit, taken from 'Carrier_Timely_Filing_Reference.xlsx'. Days Until Deadline is a live formula, so the count stays true as time passes - but the row order is a snapshot taken on 12 August 2026. Sorting on Days Until Deadline alone would mix the four groups above back together, so when you re-sort keep the Rejected rows first, then the empty Latest Date Worked rows, and the Finalized and PAID rows last.</t>
   </si>
   <si>
     <t>Where a payer had two possible limits the shorter one was used, so the real deadline can only be later, never earlier. Filing Limit and Limit Carrier name the figure applied and the carrier row it came from.</t>
@@ -2327,7 +2327,7 @@
     <t>84 claims with a date of service in 2026-04 April, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
   </si>
   <si>
-    <t>Every specialty sheet is sorted in three groups: claims with an empty Latest Date Worked (column K) at the top, then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the top group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+    <t>Every specialty sheet is sorted in four groups: Rejected claims at the very top, then claims with an empty Latest Date Worked (column K), then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the empty Latest Date Worked group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
     <t>Deadline order within each group, with the colour band each row gets, counted on 19 September 2026:</t>
@@ -3931,7 +3931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>439</v>
       </c>

--- a/SPC26S1 - 04 April.xlsx
+++ b/SPC26S1 - 04 April.xlsx
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">    3 - Due in 31+ days: 24</t>
   </si>
   <si>
-    <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 482 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+    <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 477 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
   </si>
   <si>
     <t>93923 x1; 93970 x1</t>
